--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2896,38 +2896,38 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8月28日</t>
+          <t>8月28日/10月10日</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>海大2552、混渝泰/粤海</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>—（未提及）</t>
+          <t>周公宝</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>共七口塘，计划安装料塔；日常两点半投喂；对通威业务员认可度较高、客情基础良好</t>
+          <t>七口塘，计划装料塔，对通威认可度高；老婆湖南人；主用海大2552偶混渝泰/粤海；跟周公宝拿料；主动问价，转化机会明确；与唐行平（湖南老乡）互相认识可交叉跟进。10.10客情走访。</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>B 明确意向</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>七口塘计划装料塔；对通威业务员认可度高、客情基础良好</t>
+          <t>主动问价+通威认可度高+意向明确，趁询价推通威报价</t>
         </is>
       </c>
     </row>
@@ -3305,43 +3305,43 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>丁志杰</t>
+          <t>丁志开</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9月2日</t>
+          <t>9月2日/10月10日</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>翔泰、通威</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>—（未提及）</t>
+          <t>马津深</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>大致坡乡镇039乡道基地，道路左右共5口在养鱼塘，测水发现5号塘、4号塘及马路右侧5号塘亚盐偏高，推荐降亚盐消氨氮动保</t>
+          <t>基本全程用翔泰、拉过一车通威；反映翔泰长得不行，后两月冲重量想拉通威但经销商马津深不给拉；准备拿苗原13号推迟至16号；5口塘多处亚盐偏高；其弟丁开福苗塘放60万苗（约4800尾/斤），趁早刺激快速转料用开口乐。10.10客情走访。</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>C 有潜力</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>5口塘多处亚盐偏高，已推荐降亚盐动保，服务切入</t>
+          <t>想拉通威但被经销商马津深卡住不给拉，渠道未通，潜力中等偏上</t>
         </is>
       </c>
     </row>
@@ -5348,6 +5348,98 @@
       <c r="J107" t="inlineStr">
         <is>
           <t>用户不愿意交谈</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>109</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>陈南高</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>10月10日</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>百洋（最低端）</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>—（百洋直供）</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>百洋直供用户，直接从厂里拿料不经经销商；用百洋最低端料、包产不高、转料意愿不强；其租塘明年5月到期，届时另找养户租塘续养、不找经销商（找经销商租就被绑定拿料更贵）。10.10客情走访。</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>8</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>百洋直供竞品强粘性，转料意愿弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>110</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>陈浩成</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>10月10日</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>通威（本兆前段翔泰后转通威）</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>—（公司活动拿料）</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>8月即作为通威用户参加公司饲料活动拿料；本兆前段用一点翔泰后转通威，下一兆提了一嘴要用全程通威；测水14:20塘亚盐0.15、14:23塘亚盐0.10，pH均7.4。塘口位置待确认。10.10新增用户走访。</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="n">
+        <v>50</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>提下一兆全程通威，意向明确</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5430,16 +5430,62 @@
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A 已成交/准成交</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>提下一兆全程通威，意向明确</t>
+          <t>8月起已作为通威用户持续拿料在用，下一兆提全程通威</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>111</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>唐行平</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>10.10抓鱼（出鱼期），未拜访、未交谈；养殖规模、现用料、拿料对象、地址待出鱼后回访补全；与宋平互为湖南老乡。</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>出鱼期静默，出完再联系</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -5469,7 +5469,8 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>10.10抓鱼（出鱼期），未拜访、未交谈；养殖规模、现用料、拿料对象、地址待出鱼后回访补全；与宋平互为湖南老乡。</t>
+          <t>【养殖关键节点】出鱼/抓鱼：2026-10-10（出鱼期）；放苗时间：待出鱼后回访确认。
+— 10.10抓鱼（出鱼期），未拜访、未交谈；养殖规模、现用料、拿料对象、地址待出鱼后回访补全；与宋平互为湖南老乡。</t>
         </is>
       </c>
       <c r="G110" t="n">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>8月9日修氧机、测五口塘；8月16日用9911，五六塘小鱼但亚盐偏高，推广硝消乐；8月22日三五号塘打样：9尾/斤养到三两、阶段包产78，推荐9911再用到四两，用户希望做光合扩培；9月17日现用百洋饲料，存鱼规格五两左右；10月6日测6口塘（蛟龙村3口、宝坡村2口、南阳村1口）全部达标、全场最稳，⑥号南阳村亚盐0.15最高</t>
+          <t>8月9日修氧机、测五口塘；8月16日用9911，五六塘小鱼但亚盐偏高，推广硝消乐；8月22日三五号塘打样：9尾/斤养到三两、阶段包产78，推荐9911再用到四两，用户希望做光合扩培；9月17日现用百洋饲料，存鱼规格五两左右；10月6日测6口塘（蛟龙村3口、宝坡村2口、南阳村1口）全部达标、全场最稳，⑥号南阳村亚盐0.15最高；近期新抓60万尾苗放苗（平均4800尾/斤，约125斤），与丁志开拿苗（16号节点）同期。</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>8月9日修氧机、测五口塘；8月16日用9911，五六塘小鱼但亚盐偏高，推广硝消乐；8月22日三五号塘打样：9尾/斤养到三两、阶段包产78，推荐9911再用到四两，用户希望做光合扩培；9月17日现用百洋饲料，存鱼规格五两左右；10月6日测6口塘（蛟龙村3口、宝坡村2口、南阳村1口）全部达标、全场最稳，⑥号南阳村亚盐0.15最高；近期新抓60万尾苗放苗（平均4800尾/斤，约125斤），与丁志开拿苗（16号节点）同期。</t>
+          <t>8月9日修氧机、测五口塘；8月16日用9911，五六塘小鱼但亚盐偏高，推广硝消乐；8月22日三五号塘打样：9尾/斤养到三两、阶段包产78，推荐9911再用到四两，用户希望做光合扩培；9月17日现用百洋饲料，存鱼规格五两左右；10月6日测6口塘（蛟龙村3口、宝坡村2口、南阳村1口）全部达标、全场最稳，⑥号南阳村亚盐0.15最高；9月16日新抓60万尾苗放苗（平均4800尾/斤，约125斤）。</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5490,6 +5490,52 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>112</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>黄少雄</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>10月10日（陈南高聊天获悉/本次补录）</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>翔泰</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>陈南高亲述翔泰高产样板用户（同音'黄绍雄'，电话13036004961）；现用翔泰料，包产稳定且较高，可作转介绍突破点。</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>8</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>D 竞品粘性</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>翔泰竞品高产用户，作转介绍样板，直接转料概率低</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>黄少雄</t>
+          <t>黄绍雄</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>陈南高亲述翔泰高产样板用户（同音'黄绍雄'，电话13036004961）；现用翔泰料，包产稳定且较高，可作转介绍突破点。</t>
+          <t>陈南高亲述翔泰高产样板用户（电话13036004961）；现用翔泰料，包产稳定且较高，可作转介绍突破点。</t>
         </is>
       </c>
       <c r="G111" t="n">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>—（未提及）</t>
+          <t>田永均</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -5326,7 +5326,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>—（未提及）</t>
+          <t>田永均</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -1112,7 +1112,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>周公保</t>
+          <t>周公宝</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>周公保</t>
+          <t>周公宝</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
